--- a/UAH_ASW SVT_TestProcedures.xlsx
+++ b/UAH_ASW SVT_TestProcedures.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\facud\OneDrive\Documents\GitHub\obdh_proy_26_Facundo_Dalfonso\DJF\FTs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\facud\OneDrive\Documents\GitHub\obdh_proy_26_Facundo_Dalfonso\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{22DA4BDF-D1B0-434B-8EC4-7A35904D015D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81119EA9-A294-4154-A8C7-AA4351230C50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="5" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -310,9 +310,6 @@
     <t>FT_UAH_ASW_SERV_19-0110</t>
   </si>
   <si>
-    <t>Check the FDIR mechanism that provides the PUS services ST[05], ST[12] &amp; ST[19]. Check the FDIR mechanism that provides the PUS services ST[05], ST[12] &amp; ST[19]. The test configures PMODID 0 to monitor PID 15 with a maximum limit of 20. It defines an automatic Action (Device Off) associated with the limit event 0x4002. Finally, it sets PID 15 to 99 to trigger the monitoring event and verify the automatic execution of the action.</t>
-  </si>
-  <si>
     <t>T0 + 3</t>
   </si>
   <si>
@@ -423,6 +420,9 @@
   </si>
   <si>
     <t>Check that reboot is executed</t>
+  </si>
+  <si>
+    <t>Check the FDIR mechanism that provides the PUS services ST[05], ST[12] &amp; ST[19]</t>
   </si>
 </sst>
 </file>
@@ -940,16 +940,16 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3444,7 +3444,7 @@
       </c>
     </row>
     <row r="10" spans="1:5" ht="24" customHeight="1">
-      <c r="B10" s="79" t="s">
+      <c r="B10" s="82" t="s">
         <v>40</v>
       </c>
       <c r="D10" s="25" t="s">
@@ -4562,7 +4562,7 @@
       </c>
     </row>
     <row r="10" spans="1:5" ht="24" customHeight="1">
-      <c r="B10" s="79" t="s">
+      <c r="B10" s="82" t="s">
         <v>49</v>
       </c>
       <c r="D10" s="25" t="s">
@@ -5676,7 +5676,7 @@
       </c>
     </row>
     <row r="10" spans="1:5" ht="12.75" customHeight="1">
-      <c r="B10" s="82" t="s">
+      <c r="B10" s="83" t="s">
         <v>55</v>
       </c>
       <c r="D10" s="25" t="s">
@@ -8078,7 +8078,7 @@
     </row>
     <row r="10" spans="1:5" ht="12.75" customHeight="1">
       <c r="A10" s="68"/>
-      <c r="B10" s="83" t="s">
+      <c r="B10" s="79" t="s">
         <v>81</v>
       </c>
       <c r="D10" s="65" t="s">
@@ -9222,7 +9222,7 @@
         <v>22</v>
       </c>
       <c r="B3" s="42" t="s">
-        <v>91</v>
+        <v>128</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="12.75" customHeight="1">
@@ -9232,7 +9232,7 @@
     </row>
     <row r="5" spans="1:5" ht="12.75" customHeight="1">
       <c r="A5" s="43" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B5" s="64" t="s">
         <v>52</v>
@@ -9257,10 +9257,10 @@
     <row r="7" spans="1:5" ht="12.75" customHeight="1">
       <c r="A7" s="68"/>
       <c r="B7" s="49" t="s">
+        <v>92</v>
+      </c>
+      <c r="D7" s="25" t="s">
         <v>93</v>
-      </c>
-      <c r="D7" s="25" t="s">
-        <v>94</v>
       </c>
       <c r="E7" s="69" t="s">
         <v>86</v>
@@ -9270,7 +9270,7 @@
       <c r="A8" s="68"/>
       <c r="B8" s="58"/>
       <c r="E8" s="37" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="12.75" customHeight="1">
@@ -9288,11 +9288,11 @@
     </row>
     <row r="10" spans="1:5" ht="12.75" customHeight="1">
       <c r="A10" s="68"/>
-      <c r="B10" s="83" t="s">
+      <c r="B10" s="79" t="s">
         <v>81</v>
       </c>
       <c r="D10" s="65" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E10" s="70" t="s">
         <v>42</v>
@@ -9302,7 +9302,7 @@
       <c r="A11" s="68"/>
       <c r="B11" s="80"/>
       <c r="D11" s="25" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E11" s="37" t="s">
         <v>42</v>
@@ -9312,7 +9312,7 @@
       <c r="A12" s="68"/>
       <c r="B12" s="80"/>
       <c r="D12" s="25" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E12" s="37" t="s">
         <v>42</v>
@@ -9344,22 +9344,22 @@
     <row r="15" spans="1:5" ht="12.75" customHeight="1">
       <c r="A15" s="68"/>
       <c r="B15" s="49" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C15" s="65"/>
       <c r="D15" s="65" t="s">
+        <v>99</v>
+      </c>
+      <c r="E15" s="66" t="s">
         <v>100</v>
       </c>
-      <c r="E15" s="66" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="33.75" customHeight="1">
+    </row>
+    <row r="16" spans="1:5" ht="50.4" customHeight="1">
       <c r="A16" s="68"/>
       <c r="B16" s="58"/>
       <c r="D16" s="25"/>
       <c r="E16" s="69" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="33.75" customHeight="1">
@@ -9376,11 +9376,11 @@
     </row>
     <row r="18" spans="1:5" ht="12.75" customHeight="1">
       <c r="A18" s="68"/>
-      <c r="B18" s="83" t="s">
+      <c r="B18" s="79" t="s">
         <v>81</v>
       </c>
       <c r="D18" s="65" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E18" s="70" t="s">
         <v>42</v>
@@ -9390,7 +9390,7 @@
       <c r="A19" s="68"/>
       <c r="B19" s="80"/>
       <c r="D19" s="25" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E19" s="37" t="s">
         <v>42</v>
@@ -9400,7 +9400,7 @@
       <c r="A20" s="68"/>
       <c r="B20" s="80"/>
       <c r="D20" s="25" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E20" s="37" t="s">
         <v>42</v>
@@ -9413,10 +9413,10 @@
     </row>
     <row r="22" spans="1:5" ht="12.75" customHeight="1">
       <c r="A22" s="43" t="s">
+        <v>102</v>
+      </c>
+      <c r="B22" s="72" t="s">
         <v>103</v>
-      </c>
-      <c r="B22" s="72" t="s">
-        <v>104</v>
       </c>
       <c r="C22" s="45" t="s">
         <v>31</v>
@@ -9431,14 +9431,14 @@
     <row r="23" spans="1:5" ht="12.75" customHeight="1">
       <c r="A23" s="68"/>
       <c r="B23" s="49" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C23" s="65"/>
       <c r="D23" s="65" t="s">
+        <v>105</v>
+      </c>
+      <c r="E23" s="66" t="s">
         <v>106</v>
-      </c>
-      <c r="E23" s="66" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="12.75" customHeight="1">
@@ -9446,7 +9446,7 @@
       <c r="B24" s="58"/>
       <c r="D24" s="25"/>
       <c r="E24" s="69" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="12.75" customHeight="1">
@@ -9463,11 +9463,11 @@
     </row>
     <row r="26" spans="1:5" ht="12.75" customHeight="1">
       <c r="A26" s="68"/>
-      <c r="B26" s="83" t="s">
+      <c r="B26" s="79" t="s">
         <v>81</v>
       </c>
       <c r="D26" s="65" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E26" s="70" t="s">
         <v>42</v>
@@ -9477,7 +9477,7 @@
       <c r="A27" s="68"/>
       <c r="B27" s="80"/>
       <c r="D27" s="25" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E27" s="37" t="s">
         <v>42</v>
@@ -9487,7 +9487,7 @@
       <c r="A28" s="68"/>
       <c r="B28" s="80"/>
       <c r="D28" s="25" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E28" s="37" t="s">
         <v>42</v>
@@ -9503,7 +9503,7 @@
         <v>70</v>
       </c>
       <c r="B30" s="72" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C30" s="45" t="s">
         <v>31</v>
@@ -9518,14 +9518,14 @@
     <row r="31" spans="1:5" ht="12.75" customHeight="1">
       <c r="A31" s="68"/>
       <c r="B31" s="75" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C31" s="65"/>
       <c r="D31" s="65" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E31" s="66" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="12.75" customHeight="1">
@@ -9548,11 +9548,11 @@
     </row>
     <row r="34" spans="1:5" ht="12.75" customHeight="1">
       <c r="A34" s="68"/>
-      <c r="B34" s="83" t="s">
+      <c r="B34" s="79" t="s">
         <v>81</v>
       </c>
       <c r="D34" s="65" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E34" s="70" t="s">
         <v>42</v>
@@ -9562,7 +9562,7 @@
       <c r="A35" s="68"/>
       <c r="B35" s="80"/>
       <c r="D35" s="25" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E35" s="37" t="s">
         <v>42</v>
@@ -9572,7 +9572,7 @@
       <c r="A36" s="68"/>
       <c r="B36" s="80"/>
       <c r="D36" s="25" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E36" s="37" t="s">
         <v>42</v>
@@ -9585,10 +9585,10 @@
     </row>
     <row r="38" spans="1:5" ht="12.75" customHeight="1">
       <c r="A38" s="43" t="s">
+        <v>111</v>
+      </c>
+      <c r="B38" s="72" t="s">
         <v>112</v>
-      </c>
-      <c r="B38" s="72" t="s">
-        <v>113</v>
       </c>
       <c r="C38" s="45" t="s">
         <v>31</v>
@@ -9603,14 +9603,14 @@
     <row r="39" spans="1:5" ht="12.75" customHeight="1">
       <c r="A39" s="68"/>
       <c r="B39" s="75" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C39" s="65"/>
       <c r="D39" s="65" t="s">
+        <v>114</v>
+      </c>
+      <c r="E39" s="66" t="s">
         <v>115</v>
-      </c>
-      <c r="E39" s="66" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="12.75" customHeight="1">
@@ -9633,11 +9633,11 @@
     </row>
     <row r="42" spans="1:5" ht="12.75" customHeight="1">
       <c r="A42" s="68"/>
-      <c r="B42" s="83" t="s">
+      <c r="B42" s="79" t="s">
         <v>81</v>
       </c>
       <c r="D42" s="65" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E42" s="70" t="s">
         <v>42</v>
@@ -9647,7 +9647,7 @@
       <c r="A43" s="68"/>
       <c r="B43" s="80"/>
       <c r="D43" s="25" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E43" s="37" t="s">
         <v>42</v>
@@ -9657,7 +9657,7 @@
       <c r="A44" s="68"/>
       <c r="B44" s="80"/>
       <c r="D44" s="25" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E44" s="37" t="s">
         <v>42</v>
@@ -9671,10 +9671,10 @@
     </row>
     <row r="46" spans="1:5" ht="12.75" customHeight="1">
       <c r="A46" s="43" t="s">
+        <v>116</v>
+      </c>
+      <c r="B46" s="72" t="s">
         <v>117</v>
-      </c>
-      <c r="B46" s="72" t="s">
-        <v>118</v>
       </c>
       <c r="C46" s="45" t="s">
         <v>31</v>
@@ -9689,11 +9689,11 @@
     <row r="47" spans="1:5" ht="12.75" customHeight="1">
       <c r="A47" s="68"/>
       <c r="B47" s="49" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C47" s="65"/>
       <c r="D47" s="65" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E47" s="66" t="s">
         <v>86</v>
@@ -9704,7 +9704,7 @@
       <c r="B48" s="58"/>
       <c r="D48" s="25"/>
       <c r="E48" s="69" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="12.75" customHeight="1">
@@ -9721,9 +9721,9 @@
     </row>
     <row r="50" spans="1:5" ht="12.75" customHeight="1">
       <c r="A50" s="68"/>
-      <c r="B50" s="83"/>
+      <c r="B50" s="79"/>
       <c r="D50" s="65" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E50" s="70" t="s">
         <v>42</v>
@@ -9733,7 +9733,7 @@
       <c r="A51" s="68"/>
       <c r="B51" s="80"/>
       <c r="D51" s="25" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E51" s="37" t="s">
         <v>42</v>
@@ -9743,7 +9743,7 @@
       <c r="A52" s="68"/>
       <c r="B52" s="80"/>
       <c r="D52" s="25" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E52" s="37" t="s">
         <v>42</v>
@@ -9753,10 +9753,10 @@
       <c r="A53" s="68"/>
       <c r="B53" s="81"/>
       <c r="D53" s="75" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E53" s="71" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="12.75" customHeight="1"/>
@@ -10737,7 +10737,7 @@
         <v>25</v>
       </c>
       <c r="B2" s="23" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="54" customHeight="1">
@@ -10745,7 +10745,7 @@
         <v>22</v>
       </c>
       <c r="B3" s="24" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="12.75" customHeight="1">
@@ -10755,7 +10755,7 @@
     </row>
     <row r="5" spans="1:5" ht="12.75" customHeight="1">
       <c r="A5" s="25" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B5" s="26" t="s">
         <v>30</v>
@@ -10778,10 +10778,10 @@
     </row>
     <row r="7" spans="1:5" ht="12.75" customHeight="1">
       <c r="B7" s="32" t="s">
+        <v>124</v>
+      </c>
+      <c r="D7" s="25" t="s">
         <v>125</v>
-      </c>
-      <c r="D7" s="25" t="s">
-        <v>126</v>
       </c>
       <c r="E7" s="33" t="s">
         <v>36</v>
@@ -10804,8 +10804,8 @@
       </c>
     </row>
     <row r="10" spans="1:5" ht="24" customHeight="1">
-      <c r="B10" s="79" t="s">
-        <v>127</v>
+      <c r="B10" s="82" t="s">
+        <v>126</v>
       </c>
       <c r="C10" s="76"/>
       <c r="D10" s="27" t="s">
@@ -10836,8 +10836,8 @@
       </c>
     </row>
     <row r="13" spans="1:5" ht="12.75" customHeight="1">
-      <c r="B13" s="79" t="s">
-        <v>128</v>
+      <c r="B13" s="82" t="s">
+        <v>127</v>
       </c>
       <c r="C13" s="76"/>
       <c r="D13" s="27"/>
